--- a/out/Petra Speech Logs 2025-05 May_cleaned.xlsx
+++ b/out/Petra Speech Logs 2025-05 May_cleaned.xlsx
@@ -472,13 +472,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
@@ -496,17 +496,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Week of (Monday)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date of Service</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Day of Week</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Week of (Monday)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -553,19 +553,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>05/06/2025</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2025</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Start 10:30am - End 11:00am</t>
@@ -578,7 +578,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -610,19 +610,19 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>05/06/2025</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2025</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Start 9:30am - End 10:00am</t>
@@ -635,7 +635,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -667,19 +667,19 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>05/13/2025</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>05/12/2025</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Start 9:30am - End 10:00am</t>
@@ -692,7 +692,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -724,19 +724,19 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>05/13/2025</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>05/12/2025</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Start 10:00am - End 10:30am</t>
@@ -749,7 +749,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -781,28 +781,32 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>05/19/2025</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>05/20/2025</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>05/19/2025</t>
-        </is>
-      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Start 11:00am - End 12:30pm</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Ind - Indirect</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -834,109 +838,109 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>05/19/2025</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>05/20/2025</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Start 10:00am - End 10:30am</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>G - Groups</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Group lesson: Bunny's Biscuits visual support corresponding with story for prompting WH questions - who, where, what? sentences w/ sentence frames - I want ___ biscuits, bear eats ___, eat biscuits, open, 321 blast off required prompting to express sentences -- used visual support w/ visual prompting</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Multiple Goals</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Petra Lingling Bloomer</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>05/19/2025</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Start 10:00am - End 10:30am</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>05/20/2025</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Start 9:30am - End 10:00am</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Group lesson: Bunny's Biscuits visual support corresponding with story for prompting WH questions - who, where, what? sentences w/ sentence frames - I want ___ biscuits, bear eats ___, eat biscuits, open, 321 blast off required prompting to express sentences -- used visual support w/ visual prompting</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Supported communication during classroom activity difficulty establishing engagement - required tactile and verbal prompting to return to designated space. She attempted to climb cubby - stopped with verbal prompting. responding to greeting -- responded verbally after 3 repetitions who is here/.where are you? prompted to use AAC device to respond "school" -- Petra went to animal/sounds page and touched corresponding buttons. When provided model to change page, she said "no!" - indicating protest responded to questions re: weather w/ sentence starter "it is..."</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Petra Lingling Bloomer</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>05/27/2025</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>05/26/2025</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Start 9:30am - End 10:00am</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>E - Clinician/Therapist Unavailable</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>am</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>SLP @ IEP Meeting</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>(BLANK)</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>(BLANK)</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>No Goal</t>
         </is>
       </c>
     </row>
@@ -948,50 +952,107 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>05/26/2025</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>05/27/2025</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Start 9:30am - End 10:00am</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>E - Clinician/Therapist Unavailable</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>SLP @ IEP Meeting</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>No Goal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Petra Lingling Bloomer</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>05/26/2025</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>05/27/2025</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>E - Clinician/Therapist Unavailable</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>(BLANK)</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>SLP @ IEP meeting</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>(BLANK)</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>(BLANK)</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
